--- a/data/trans_dic/P36B08_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P36B08_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,16%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>65,94; 74,4</t>
+          <t>65,15; 73,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>73,31; 81,79</t>
+          <t>73,01; 81,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>74,59; 83,25</t>
+          <t>74,24; 82,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>94,39; 97,73</t>
+          <t>94,58; 97,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>68,88; 79,03</t>
+          <t>69,36; 79,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,07; 90,84</t>
+          <t>82,97; 90,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,72; 85,87</t>
+          <t>77,71; 86,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>97,05; 99,3</t>
+          <t>96,04; 99,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>68,35; 74,81</t>
+          <t>68,33; 75,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>78,45; 84,42</t>
+          <t>78,7; 84,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>76,98; 83,02</t>
+          <t>77,03; 83,21</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,01; 98,18</t>
+          <t>95,85; 98,1</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,41%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>59,35; 69,22</t>
+          <t>59,5; 69,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>70,21; 79,33</t>
+          <t>70,39; 79,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73,68; 82,77</t>
+          <t>73,71; 82,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92,72; 97,04</t>
+          <t>93,21; 97,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>63,93; 73,48</t>
+          <t>64,03; 73,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,91; 83,76</t>
+          <t>73,98; 83,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,66; 83,42</t>
+          <t>74,69; 82,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>94,44; 98,42</t>
+          <t>95,05; 98,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>63,19; 70,18</t>
+          <t>63,0; 70,18</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>73,33; 80,18</t>
+          <t>73,49; 80,05</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75,77; 81,72</t>
+          <t>75,98; 81,85</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>94,54; 97,34</t>
+          <t>94,85; 97,6</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>95,23%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>58,22; 66,31</t>
+          <t>58,09; 66,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>70,71; 77,52</t>
+          <t>70,82; 77,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>65,85; 74,25</t>
+          <t>66,03; 74,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>94,02; 99,06</t>
+          <t>92,65; 96,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>62,04; 76,61</t>
+          <t>62,26; 76,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>75,02; 85,33</t>
+          <t>75,26; 85,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>72,68; 85,98</t>
+          <t>73,06; 85,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>91,7; 97,62</t>
+          <t>91,72; 97,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>60,44; 67,72</t>
+          <t>60,51; 67,43</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>73,37; 79,12</t>
+          <t>72,87; 78,86</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>68,65; 75,59</t>
+          <t>69,07; 75,94</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>94,44; 98,69</t>
+          <t>93,32; 96,77</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,56%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>61,95; 67,66</t>
+          <t>61,65; 67,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>68,09; 73,46</t>
+          <t>67,92; 73,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>68,27; 73,76</t>
+          <t>68,31; 73,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>92,04; 95,28</t>
+          <t>92,32; 95,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>67,63; 74,42</t>
+          <t>67,7; 74,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,92; 81,51</t>
+          <t>75,18; 81,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,9; 78,83</t>
+          <t>72,95; 78,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>94,38; 98,19</t>
+          <t>93,76; 96,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>65,08; 69,06</t>
+          <t>64,92; 68,86</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71,95; 75,96</t>
+          <t>71,65; 75,8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>71,16; 75,12</t>
+          <t>71,11; 75,13</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,68; 96,49</t>
+          <t>93,45; 95,46</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,3%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>52,84; 63,76</t>
+          <t>52,75; 63,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>66,01; 74,16</t>
+          <t>66,61; 74,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68,26; 75,97</t>
+          <t>68,86; 76,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>88,7; 94,8</t>
+          <t>90,07; 95,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>66,82; 74,7</t>
+          <t>66,8; 74,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>75,42; 81,56</t>
+          <t>75,67; 81,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,93; 80,93</t>
+          <t>74,57; 80,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>93,85; 96,68</t>
+          <t>93,87; 96,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>62,99; 69,22</t>
+          <t>62,87; 69,31</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>72,47; 77,6</t>
+          <t>72,81; 77,74</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73,12; 77,62</t>
+          <t>73,13; 77,89</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>92,78; 95,8</t>
+          <t>92,88; 95,44</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,9%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>46,39; 57,72</t>
+          <t>46,13; 57,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>43,88; 56,3</t>
+          <t>43,98; 56,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>56,97; 68,78</t>
+          <t>56,22; 67,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>77,81; 94,11</t>
+          <t>81,56; 94,43</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>68,59; 73,7</t>
+          <t>68,46; 73,49</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>76,18; 81,37</t>
+          <t>75,97; 81,1</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>72,91; 78,3</t>
+          <t>72,74; 77,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>92,1; 95,99</t>
+          <t>93,28; 96,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>65,04; 69,57</t>
+          <t>64,91; 69,82</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>70,56; 75,73</t>
+          <t>70,96; 75,58</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>70,42; 75,4</t>
+          <t>70,37; 75,23</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>90,48; 94,91</t>
+          <t>91,85; 95,51</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>61,39; 64,8</t>
+          <t>61,55; 64,96</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>69,47; 72,7</t>
+          <t>69,5; 72,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>70,79; 73,95</t>
+          <t>70,79; 73,84</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>93,3; 95,68</t>
+          <t>93,25; 95,18</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>69,68; 72,58</t>
+          <t>69,42; 72,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,14; 80,85</t>
+          <t>78,17; 80,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,86; 78,78</t>
+          <t>76,03; 78,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>95,13; 96,7</t>
+          <t>95,14; 96,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>66,08; 68,34</t>
+          <t>65,98; 68,28</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>74,36; 76,48</t>
+          <t>74,38; 76,54</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>73,8; 75,9</t>
+          <t>73,89; 76,0</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,55; 95,97</t>
+          <t>94,54; 95,61</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>486122</t>
+          <t>530889</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>440569</t>
+          <t>478634</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>926691</t>
+          <t>1009523</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>311854; 351856</t>
+          <t>308104; 348904</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>318973; 355873</t>
+          <t>317653; 356422</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>320046; 357214</t>
+          <t>318546; 355902</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>476882; 493732</t>
+          <t>520800; 538545</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>211237; 242376</t>
+          <t>212723; 243326</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>259610; 283884</t>
+          <t>259304; 283920</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>268935; 297150</t>
+          <t>268927; 298428</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>434252; 444337</t>
+          <t>469083; 483780</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>532880; 583238</t>
+          <t>532703; 585164</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>586517; 631111</t>
+          <t>588349; 631567</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>596667; 643501</t>
+          <t>597060; 644997</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>914641; 935309</t>
+          <t>995881; 1019262</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>430661</t>
+          <t>461482</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>370159</t>
+          <t>410675</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>800821</t>
+          <t>872157</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>217764; 253995</t>
+          <t>218315; 256362</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>293331; 331409</t>
+          <t>294083; 330974</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>277139; 311328</t>
+          <t>277262; 309732</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>418620; 438133</t>
+          <t>449722; 469668</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>237741; 273234</t>
+          <t>238111; 273703</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>247678; 280706</t>
+          <t>247926; 278783</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>274670; 306912</t>
+          <t>274809; 305187</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>360492; 375673</t>
+          <t>401265; 415853</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>466842; 518458</t>
+          <t>465474; 518495</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>552081; 603684</t>
+          <t>553292; 602657</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>563776; 608055</t>
+          <t>565304; 609040</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>787703; 811039</t>
+          <t>858051; 882959</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>647127</t>
+          <t>448960</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>158735</t>
+          <t>178678</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>805862</t>
+          <t>627637</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>315776; 359672</t>
+          <t>315073; 362034</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>445075; 487942</t>
+          <t>445769; 489244</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>343669; 387504</t>
+          <t>344640; 386206</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>628299; 661981</t>
+          <t>436967; 456772</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>104091; 128536</t>
+          <t>104456; 128176</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>195140; 221970</t>
+          <t>195768; 221988</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>120054; 142024</t>
+          <t>120685; 141160</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>153051; 162931</t>
+          <t>171973; 182808</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>429262; 480908</t>
+          <t>429755; 478880</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>652701; 703789</t>
+          <t>648218; 701465</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>471663; 519366</t>
+          <t>474551; 521768</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>788699; 824199</t>
+          <t>615099; 637835</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>969591</t>
+          <t>1061838</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>939095</t>
+          <t>819520</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1908685</t>
+          <t>1881358</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>767099; 837807</t>
+          <t>763443; 832083</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>787098; 849226</t>
+          <t>785107; 849774</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>777382; 839838</t>
+          <t>777829; 837499</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>950824; 984371</t>
+          <t>1042278; 1078150</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>483070; 531582</t>
+          <t>483581; 530553</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>571529; 621785</t>
+          <t>573462; 621053</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>600592; 649430</t>
+          <t>600981; 649264</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>922543; 959817</t>
+          <t>806942; 830357</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1270810; 1348543</t>
+          <t>1267736; 1344566</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1380476; 1457434</t>
+          <t>1374781; 1454490</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1396541; 1474303</t>
+          <t>1395478; 1474421</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1883582; 1940012</t>
+          <t>1859227; 1899307</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>437662</t>
+          <t>527707</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>801800</t>
+          <t>788969</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1239463</t>
+          <t>1316677</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>185217; 223525</t>
+          <t>184911; 222810</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>336331; 377862</t>
+          <t>339377; 380064</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>420949; 468479</t>
+          <t>424644; 469092</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>420457; 449381</t>
+          <t>510601; 539073</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>379341; 424079</t>
+          <t>379214; 424792</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>573502; 620163</t>
+          <t>575364; 620940</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>551561; 595684</t>
+          <t>548922; 595706</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>788303; 812054</t>
+          <t>778571; 799123</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>578446; 635641</t>
+          <t>577338; 636425</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>920348; 985501</t>
+          <t>924665; 987249</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>989106; 1050011</t>
+          <t>989318; 1053671</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1219133; 1258746</t>
+          <t>1296923; 1332660</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>213509</t>
+          <t>212503</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>718749</t>
+          <t>801945</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>932258</t>
+          <t>1014448</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>138331; 172121</t>
+          <t>137554; 171814</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>117104; 150264</t>
+          <t>117366; 151485</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>162969; 196747</t>
+          <t>160827; 193749</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>187127; 226351</t>
+          <t>193489; 224010</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>856557; 920385</t>
+          <t>854946; 917681</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>845127; 902698</t>
+          <t>842755; 899735</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>784324; 842266</t>
+          <t>782501; 838394</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>700207; 729772</t>
+          <t>786472; 813110</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1006187; 1076167</t>
+          <t>1004167; 1080139</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>971127; 1042287</t>
+          <t>976549; 1040121</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>959037; 1026746</t>
+          <t>958376; 1024546</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>905557; 949889</t>
+          <t>992315; 1031837</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3184673</t>
+          <t>3243379</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>3429108</t>
+          <t>3478421</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>6613779</t>
+          <t>6721799</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2006985; 2118644</t>
+          <t>2012438; 2123701</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2372312; 2482438</t>
+          <t>2373211; 2483639</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2384541; 2491044</t>
+          <t>2384673; 2487409</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3146565; 3226942</t>
+          <t>3205902; 3272207</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2353144; 2451232</t>
+          <t>2344268; 2452546</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2766415; 2862267</t>
+          <t>2767298; 2865881</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2666289; 2768926</t>
+          <t>2672482; 2772422</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>3399829; 3455855</t>
+          <t>3454700; 3500906</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4392089; 4542456</t>
+          <t>4385553; 4538443</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5171504; 5318948</t>
+          <t>5172903; 5323110</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5079833; 5224452</t>
+          <t>5086086; 5231360</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>6567601; 6666366</t>
+          <t>6683069; 6758983</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36B08_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P36B08_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas (tasa de respuesta: 99,79%)</t>
+          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas  [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales] (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas (tasa de respuesta: 99,79%)</t>
+          <t>Población que consume 3 veces o más a la semana verduras, ensaladas y hortalizas  [2023 pregunta frecuencias diarias, ediciones anteriores frecuencias semanales] (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
